--- a/salidas/empresas/SNDK.xlsx
+++ b/salidas/empresas/SNDK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B3" t="n">
@@ -526,7 +538,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B4" t="n">
@@ -551,7 +563,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B5" t="n">
@@ -576,7 +588,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B6" t="n">
@@ -601,7 +613,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B7" t="n">
@@ -626,7 +638,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B8" t="n">
@@ -651,7 +663,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B9" t="n">
@@ -676,7 +688,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B10" t="n">
@@ -701,7 +713,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B11" t="n">
@@ -726,7 +738,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B12" t="n">
@@ -751,7 +763,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B13" t="n">
@@ -778,7 +790,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B14" t="n">
@@ -805,7 +817,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B15" t="n">
@@ -832,7 +844,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B16" t="n">
@@ -859,7 +871,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B17" t="n">
@@ -888,7 +900,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B18" t="n">
@@ -917,7 +929,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B19" t="n">
@@ -946,7 +958,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B20" t="n">
@@ -975,32 +987,32 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B21" t="n">
-        <v>1816.569946289062</v>
+        <v>1753.619995117188</v>
       </c>
       <c r="C21" t="n">
-        <v>1816.569946289062</v>
+        <v>1753.619995117188</v>
       </c>
       <c r="D21" t="n">
-        <v>166004300</v>
+        <v>174235400</v>
       </c>
       <c r="E21" t="n">
         <v>73.76000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>24.62811749307297</v>
+        <v>23.7746745541918</v>
       </c>
       <c r="G21" t="n">
         <v>146419001</v>
       </c>
       <c r="H21" t="n">
-        <v>265980356782.2682</v>
+        <v>256763287818.6835</v>
       </c>
       <c r="I21" t="n">
-        <v>1.133762004017498</v>
+        <v>1.189978068488529</v>
       </c>
     </row>
   </sheetData>
@@ -1032,75 +1044,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45290</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>45380</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -1136,13 +1148,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45381</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>45471</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -1178,13 +1190,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45472</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>45562</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -1220,13 +1232,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45563</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>45653</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -1253,7 +1265,7 @@
       <c r="I5" t="n">
         <v>3.197586206896552</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K5" t="n">
@@ -1266,13 +1278,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>45654</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>45744</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -1299,7 +1311,7 @@
       <c r="I6" t="n">
         <v>-10.32241379310345</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K6" t="n">
@@ -1312,13 +1324,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>45745</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>45835</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -1345,7 +1357,7 @@
       <c r="I7" t="n">
         <v>-11.30862068965517</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K7" t="n">
@@ -1358,13 +1370,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>45836</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>45933</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -1391,7 +1403,7 @@
       <c r="I8" t="n">
         <v>-12.01862068965517</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K8" t="n">
@@ -1404,13 +1416,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>45934</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>46024</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -1437,7 +1449,7 @@
       <c r="I9" t="n">
         <v>-7.588620689655172</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="K9" t="n">
@@ -1450,13 +1462,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>46025</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>46115</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -1483,7 +1495,7 @@
       <c r="I10" t="n">
         <v>28.77137931034483</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="K10" t="n">
@@ -1496,13 +1508,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>46116</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>46206</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>46251</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -1529,7 +1541,7 @@
       <c r="I11" t="n">
         <v>73.76000000000001</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>46251</v>
       </c>
       <c r="K11" t="n">
@@ -1566,52 +1578,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>45715</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>45723</v>
       </c>
       <c r="C2" t="n">
@@ -1640,10 +1652,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>45782</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>45789</v>
       </c>
       <c r="C3" t="n">
@@ -1672,10 +1684,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>45882</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>45890</v>
       </c>
       <c r="C4" t="n">
@@ -1704,10 +1716,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>45961</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>45968</v>
       </c>
       <c r="C5" t="n">
@@ -1736,10 +1748,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>46045</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>46052</v>
       </c>
       <c r="C6" t="n">
@@ -1768,10 +1780,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>46136</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>46143</v>
       </c>
       <c r="C7" t="n">
@@ -1800,10 +1812,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>46241</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>46251</v>
       </c>
       <c r="C8" t="n">
@@ -1850,12 +1862,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
